--- a/src/views/game/zlzq/cardList/taotailangCard/z_level.xlsx
+++ b/src/views/game/zlzq/cardList/taotailangCard/z_level.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="11790" windowHeight="10800" firstSheet="1" activeTab="1"/>
+    <workbookView windowWidth="11190" windowHeight="9990" firstSheet="1" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="蛮石" sheetId="8" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="53">
   <si>
     <t>名称</t>
   </si>
@@ -62,21 +62,18 @@
     <t>暴怒野人</t>
   </si>
   <si>
-    <t>肥鼠晚宴</t>
-  </si>
-  <si>
     <t>活力仙人掌</t>
   </si>
   <si>
-    <t>地洞巨獾</t>
+    <t>肥鼠晚宴1</t>
+  </si>
+  <si>
+    <t>肥鼠晚宴2</t>
   </si>
   <si>
     <t>飞斧狂人</t>
   </si>
   <si>
-    <t>源力苏醒</t>
-  </si>
-  <si>
     <t>贪食白龙</t>
   </si>
   <si>
@@ -158,6 +155,9 @@
     <t>龟族僧人</t>
   </si>
   <si>
+    <t>执剑道者</t>
+  </si>
+  <si>
     <t>连击1</t>
   </si>
   <si>
@@ -167,18 +167,12 @@
     <t>连击3</t>
   </si>
   <si>
-    <t>执剑道者</t>
-  </si>
-  <si>
     <t>铁山靠1</t>
   </si>
   <si>
     <t>铁山靠2</t>
   </si>
   <si>
-    <t>风铃道人</t>
-  </si>
-  <si>
     <t>风卷残云</t>
   </si>
   <si>
@@ -189,12 +183,6 @@
   </si>
   <si>
     <t>泰山之力</t>
-  </si>
-  <si>
-    <t>蟠桃会</t>
-  </si>
-  <si>
-    <t>万物之灵</t>
   </si>
   <si>
     <t>神机玄女·轩</t>
@@ -1164,7 +1152,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="16.375" customWidth="1"/>
@@ -1172,7 +1160,7 @@
     <col min="3" max="3" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1183,7 +1171,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -1194,7 +1182,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -1202,10 +1190,10 @@
         <v>2</v>
       </c>
       <c r="C3" s="1">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -1216,7 +1204,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
@@ -1224,10 +1212,10 @@
         <v>3</v>
       </c>
       <c r="C5" s="1">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
@@ -1235,15 +1223,15 @@
         <v>4</v>
       </c>
       <c r="C6" s="1">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:4">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
@@ -1257,11 +1245,11 @@
       </c>
       <c r="C9" s="1">
         <f>AVERAGE(C2:C6)</f>
-        <v>20.4</v>
+        <v>21.4</v>
       </c>
       <c r="D9" s="2"/>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:4">
       <c r="A12" s="2" t="s">
         <v>9</v>
       </c>
@@ -1272,7 +1260,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:4">
       <c r="A13" s="2" t="s">
         <v>10</v>
       </c>
@@ -1280,10 +1268,10 @@
         <v>3</v>
       </c>
       <c r="C13" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
       <c r="A14" s="2" t="s">
         <v>11</v>
       </c>
@@ -1291,10 +1279,10 @@
         <v>3</v>
       </c>
       <c r="C14" s="2">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
       <c r="A15" s="2" t="s">
         <v>12</v>
       </c>
@@ -1302,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C15" s="2">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
       <c r="A16" s="2" t="s">
         <v>13</v>
       </c>
@@ -1313,7 +1301,7 @@
         <v>4</v>
       </c>
       <c r="C16" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -1321,22 +1309,16 @@
         <v>14</v>
       </c>
       <c r="B17" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C17" s="2">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18" spans="1:3">
-      <c r="A18" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B18" s="2">
-        <v>8</v>
-      </c>
-      <c r="C18" s="2">
-        <v>21</v>
-      </c>
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2"/>
@@ -1344,20 +1326,26 @@
       <c r="C19" s="2"/>
     </row>
     <row r="20" spans="1:3">
-      <c r="A20" s="2"/>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" s="2" t="s">
+      <c r="A20" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="B20" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C20" s="2">
+        <f>AVERAGE(C12:C17)</f>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C21" s="2">
-        <f>AVERAGE(C12:C18)</f>
-        <v>19.4285714285714</v>
+      <c r="B23" s="3">
+        <v>3</v>
+      </c>
+      <c r="C23" s="3">
+        <v>15</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -1365,10 +1353,10 @@
         <v>17</v>
       </c>
       <c r="B24" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C24" s="3">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1376,10 +1364,10 @@
         <v>18</v>
       </c>
       <c r="B25" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C25" s="3">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1387,22 +1375,16 @@
         <v>19</v>
       </c>
       <c r="B26" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C26" s="3">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="27" spans="1:3">
-      <c r="A27" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B27" s="3">
-        <v>8</v>
-      </c>
-      <c r="C27" s="3">
-        <v>15</v>
-      </c>
+      <c r="A27" s="3"/>
+      <c r="B27" s="3"/>
+      <c r="C27" s="3"/>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="3"/>
@@ -1410,32 +1392,27 @@
       <c r="C28" s="3"/>
     </row>
     <row r="29" spans="1:3">
-      <c r="A29" s="3"/>
-      <c r="B29" s="3"/>
-      <c r="C29" s="3"/>
-    </row>
-    <row r="30" spans="1:3">
-      <c r="A30" s="3" t="s">
+      <c r="A29" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="B29" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C29" s="3">
+        <f>AVERAGE(C23:C26)</f>
+        <v>17.25</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C30" s="3">
-        <f>AVERAGE(C24:C27)</f>
-        <v>16.25</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3">
-      <c r="A33" s="4" t="s">
+      <c r="B32" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B33" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C33" s="4">
-        <f>AVERAGE(C2:C6,C12:C18,C24:C27)</f>
-        <v>18.9375</v>
+      <c r="C32" s="4">
+        <f>AVERAGE(C2:C6,C12:C17,C23:C26)</f>
+        <v>20.1333333333333</v>
       </c>
     </row>
   </sheetData>
@@ -1455,7 +1432,7 @@
     <col min="3" max="3" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1466,42 +1443,42 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B2" s="1">
         <v>2</v>
       </c>
       <c r="C2" s="1">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B3" s="1">
         <v>2</v>
       </c>
       <c r="C3" s="1">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B4" s="1">
         <v>3</v>
       </c>
       <c r="C4" s="1">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B5" s="1">
         <v>5</v>
@@ -1510,12 +1487,12 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:4">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:4">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
@@ -1529,24 +1506,24 @@
       </c>
       <c r="C8" s="1">
         <f>AVERAGE(C2:C5)</f>
-        <v>17.75</v>
+        <v>18.75</v>
       </c>
       <c r="D8" s="2"/>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:4">
       <c r="A11" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B11" s="2">
         <v>2</v>
       </c>
       <c r="C11" s="2">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
       <c r="A12" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B12" s="2">
         <v>2</v>
@@ -1555,31 +1532,31 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:4">
       <c r="A13" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B13" s="2">
         <v>4</v>
       </c>
       <c r="C13" s="2">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
       <c r="A14" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B14" s="2">
         <v>6</v>
       </c>
       <c r="C14" s="2">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
       <c r="A15" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B15" s="2">
         <v>7</v>
@@ -1588,26 +1565,26 @@
         <v>22</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:4">
       <c r="A16" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B16" s="2">
         <v>7</v>
       </c>
       <c r="C16" s="2">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B17" s="2">
         <v>9</v>
       </c>
       <c r="C17" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1625,16 +1602,16 @@
         <v>7</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C20" s="2">
         <f>AVERAGE(C11:C17)</f>
-        <v>17.7142857142857</v>
+        <v>18.7142857142857</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B23" s="3">
         <v>5</v>
@@ -1645,18 +1622,18 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B24" s="3">
         <v>6</v>
       </c>
       <c r="C24" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B25" s="3">
         <v>7</v>
@@ -1667,13 +1644,13 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B26" s="3">
         <v>9</v>
       </c>
       <c r="C26" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1691,23 +1668,23 @@
         <v>7</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C29" s="3">
         <f>AVERAGE(C23:C26)</f>
-        <v>16</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C32" s="4">
         <f>AVERAGE(C2:C5,C11:C17,C23:C26)</f>
-        <v>17.2666666666667</v>
+        <v>18.1333333333333</v>
       </c>
     </row>
   </sheetData>
@@ -1719,7 +1696,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D35"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="17.75" customWidth="1"/>
@@ -1727,7 +1704,7 @@
     <col min="3" max="3" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1738,9 +1715,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B2" s="1">
         <v>2</v>
@@ -1749,9 +1726,9 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B3" s="1">
         <v>2</v>
@@ -1760,31 +1737,31 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B4" s="1">
         <v>3</v>
       </c>
       <c r="C4" s="1">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B5" s="1">
         <v>3</v>
       </c>
       <c r="C5" s="1">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B6" s="1">
         <v>3</v>
@@ -1793,31 +1770,31 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B7" s="1">
         <v>3</v>
       </c>
       <c r="C7" s="1">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B8" s="1">
         <v>3</v>
       </c>
       <c r="C8" s="1">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B9" s="1">
         <v>3</v>
@@ -1826,9 +1803,9 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B10" s="1">
         <v>3</v>
@@ -1837,9 +1814,9 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B11" s="1">
         <v>4</v>
@@ -1848,56 +1825,54 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B12" s="1">
-        <v>4</v>
-      </c>
-      <c r="C12" s="1">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
+    <row r="12" spans="1:4">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+    </row>
+    <row r="13" spans="1:4">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
     </row>
-    <row r="14" spans="1:3">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" s="1" t="s">
+    <row r="14" spans="1:4">
+      <c r="A14" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B14" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="1">
-        <f>AVERAGE(C2:C12)</f>
-        <v>13.1818181818182</v>
-      </c>
-      <c r="D15" s="2"/>
-    </row>
-    <row r="16" customFormat="1"/>
-    <row r="17" customFormat="1"/>
+      <c r="C14" s="1">
+        <f>AVERAGE(C2:C11)</f>
+        <v>13.5</v>
+      </c>
+      <c r="D14" s="2"/>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B17" s="2">
+        <v>4</v>
+      </c>
+      <c r="C17" s="2">
+        <v>16</v>
+      </c>
+    </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B18" s="2">
         <v>4</v>
       </c>
       <c r="C18" s="2">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B19" s="2">
         <v>4</v>
@@ -1907,118 +1882,81 @@
       </c>
     </row>
     <row r="20" spans="1:3">
-      <c r="A20" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B20" s="2">
-        <v>4</v>
-      </c>
-      <c r="C20" s="2">
-        <v>12</v>
-      </c>
+      <c r="A20" s="2"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
     </row>
     <row r="21" spans="1:3">
-      <c r="A21" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B21" s="2">
-        <v>4</v>
-      </c>
-      <c r="C21" s="2">
-        <v>12</v>
-      </c>
+      <c r="A21" s="2"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B22" s="2">
-        <v>5</v>
+        <v>7</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="C22" s="2">
+        <f>AVERAGE(C17:C19)</f>
+        <v>13.3333333333333</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B25" s="3">
+        <v>4</v>
+      </c>
+      <c r="C25" s="3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B26" s="3">
+        <v>4</v>
+      </c>
+      <c r="C26" s="3">
         <v>12</v>
       </c>
     </row>
-    <row r="23" spans="1:3">
-      <c r="A23" s="2"/>
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-    </row>
-    <row r="24" spans="1:3">
-      <c r="A24" s="2"/>
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-    </row>
-    <row r="25" spans="1:3">
-      <c r="A25" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C25" s="2">
-        <f>AVERAGE(C18:C22)</f>
-        <v>12.6</v>
-      </c>
-    </row>
-    <row r="26" customFormat="1"/>
-    <row r="27" customFormat="1"/>
+    <row r="27" spans="1:3">
+      <c r="A27" s="3"/>
+      <c r="B27" s="3"/>
+      <c r="C27" s="3"/>
+    </row>
     <row r="28" spans="1:3">
-      <c r="A28" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="B28" s="3">
-        <v>4</v>
-      </c>
-      <c r="C28" s="3">
-        <v>13</v>
-      </c>
+      <c r="A28" s="3"/>
+      <c r="B28" s="3"/>
+      <c r="C28" s="3"/>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="B29" s="3">
-        <v>4</v>
+        <v>7</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>20</v>
       </c>
       <c r="C29" s="3">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3">
-      <c r="A30" s="3"/>
-      <c r="B30" s="3"/>
-      <c r="C30" s="3"/>
-    </row>
-    <row r="31" spans="1:3">
-      <c r="A31" s="3"/>
-      <c r="B31" s="3"/>
-      <c r="C31" s="3"/>
+        <f>AVERAGE(C25:C26)</f>
+        <v>13.5</v>
+      </c>
     </row>
     <row r="32" spans="1:3">
-      <c r="A32" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B32" s="3" t="s">
+      <c r="A32" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C32" s="3">
-        <f>AVERAGE(C28:C29)</f>
-        <v>12.5</v>
-      </c>
-    </row>
-    <row r="33" customFormat="1"/>
-    <row r="34" customFormat="1"/>
-    <row r="35" spans="1:3">
-      <c r="A35" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B35" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="C35" s="4">
-        <f>AVERAGE(C2:C12,C18:C22,C28:C29)</f>
-        <v>12.9444444444444</v>
+      <c r="B32" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C32" s="4">
+        <f>AVERAGE(C2:C11,C17:C19,C25:C26)</f>
+        <v>13.4666666666667</v>
       </c>
     </row>
   </sheetData>
